--- a/data/nzd0571/nzd0571.xlsx
+++ b/data/nzd0571/nzd0571.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S449"/>
+  <dimension ref="A1:S450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28741,6 +28741,69 @@
       <c r="S449" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:25+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>262.39</v>
+      </c>
+      <c r="C450" t="n">
+        <v>260.97</v>
+      </c>
+      <c r="D450" t="n">
+        <v>254.94</v>
+      </c>
+      <c r="E450" t="n">
+        <v>255.7</v>
+      </c>
+      <c r="F450" t="n">
+        <v>253.23</v>
+      </c>
+      <c r="G450" t="n">
+        <v>255.71</v>
+      </c>
+      <c r="H450" t="n">
+        <v>258.78</v>
+      </c>
+      <c r="I450" t="n">
+        <v>261.22</v>
+      </c>
+      <c r="J450" t="n">
+        <v>263.74</v>
+      </c>
+      <c r="K450" t="n">
+        <v>264.97</v>
+      </c>
+      <c r="L450" t="n">
+        <v>260.99</v>
+      </c>
+      <c r="M450" t="n">
+        <v>268.47</v>
+      </c>
+      <c r="N450" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="O450" t="n">
+        <v>276.82</v>
+      </c>
+      <c r="P450" t="n">
+        <v>275.67</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>284.02</v>
+      </c>
+      <c r="R450" t="n">
+        <v>276.68</v>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28755,7 +28818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B462"/>
+  <dimension ref="A1:B463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33378,6 +33441,16 @@
       </c>
       <c r="B462" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -33540,28 +33613,28 @@
         <v>0.0407</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4313771325868206</v>
+        <v>-0.4314396955113928</v>
       </c>
       <c r="J2" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K2" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2088890142089811</v>
+        <v>0.2098382246629781</v>
       </c>
       <c r="M2" t="n">
-        <v>4.492061416720775</v>
+        <v>4.482372146765901</v>
       </c>
       <c r="N2" t="n">
-        <v>38.61419134128133</v>
+        <v>38.52823031848719</v>
       </c>
       <c r="O2" t="n">
-        <v>6.214031810449745</v>
+        <v>6.207111270026274</v>
       </c>
       <c r="P2" t="n">
-        <v>274.1136728070273</v>
+        <v>274.1143333024777</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33612,28 +33685,28 @@
         <v>0.0375</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3230997153860037</v>
+        <v>-0.3227628328725139</v>
       </c>
       <c r="J3" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K3" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1052025285398661</v>
+        <v>0.1055169203631013</v>
       </c>
       <c r="M3" t="n">
-        <v>5.112211721569904</v>
+        <v>5.102185097579519</v>
       </c>
       <c r="N3" t="n">
-        <v>48.64997388869316</v>
+        <v>48.54276455336762</v>
       </c>
       <c r="O3" t="n">
-        <v>6.974953325198181</v>
+        <v>6.96726377808158</v>
       </c>
       <c r="P3" t="n">
-        <v>268.932240269062</v>
+        <v>268.9286836999115</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33684,28 +33757,28 @@
         <v>0.0406</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3753225372624741</v>
+        <v>-0.3755269621085064</v>
       </c>
       <c r="J4" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K4" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1146967949893415</v>
+        <v>0.1153612551085829</v>
       </c>
       <c r="M4" t="n">
-        <v>5.31247262695894</v>
+        <v>5.301689010165667</v>
       </c>
       <c r="N4" t="n">
-        <v>59.57457212233356</v>
+        <v>59.44231002780308</v>
       </c>
       <c r="O4" t="n">
-        <v>7.71845658939231</v>
+        <v>7.709883917920106</v>
       </c>
       <c r="P4" t="n">
-        <v>265.4649846019134</v>
+        <v>265.4671427759708</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33756,28 +33829,28 @@
         <v>0.0409</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.30082459861185</v>
+        <v>-0.3013979371853034</v>
       </c>
       <c r="J5" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K5" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08814658789890784</v>
+        <v>0.08888795752307543</v>
       </c>
       <c r="M5" t="n">
-        <v>4.690663625459467</v>
+        <v>4.683273188494776</v>
       </c>
       <c r="N5" t="n">
-        <v>51.29288232604107</v>
+        <v>51.18195346882892</v>
       </c>
       <c r="O5" t="n">
-        <v>7.161904936959235</v>
+        <v>7.154156377157891</v>
       </c>
       <c r="P5" t="n">
-        <v>265.0042149545627</v>
+        <v>265.0102678608474</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33828,28 +33901,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4008634983829556</v>
+        <v>-0.402609631350098</v>
       </c>
       <c r="J6" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K6" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2210562182807916</v>
+        <v>0.2233283435420736</v>
       </c>
       <c r="M6" t="n">
-        <v>4.229109816973027</v>
+        <v>4.226068949424115</v>
       </c>
       <c r="N6" t="n">
-        <v>31.02467879490838</v>
+        <v>30.98627553314508</v>
       </c>
       <c r="O6" t="n">
-        <v>5.569980143134119</v>
+        <v>5.566531732878659</v>
       </c>
       <c r="P6" t="n">
-        <v>267.7297368397561</v>
+        <v>267.7481712861724</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33900,28 +33973,28 @@
         <v>0.0404</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6297582680071442</v>
+        <v>-0.6299020326588487</v>
       </c>
       <c r="J7" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K7" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3012202077657963</v>
+        <v>0.3024630535480091</v>
       </c>
       <c r="M7" t="n">
-        <v>5.116147951004386</v>
+        <v>5.10536357099377</v>
       </c>
       <c r="N7" t="n">
-        <v>50.4097890624974</v>
+        <v>50.29772588444265</v>
       </c>
       <c r="O7" t="n">
-        <v>7.099985145230757</v>
+        <v>7.092088964786232</v>
       </c>
       <c r="P7" t="n">
-        <v>272.9394173132947</v>
+        <v>272.9409350795921</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33972,28 +34045,28 @@
         <v>0.0415</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4599140034175053</v>
+        <v>-0.4588646232814018</v>
       </c>
       <c r="J8" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K8" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1917075838542841</v>
+        <v>0.191808233403133</v>
       </c>
       <c r="M8" t="n">
-        <v>5.199034037857801</v>
+        <v>5.192413219326397</v>
       </c>
       <c r="N8" t="n">
-        <v>48.86448964323002</v>
+        <v>48.76674578784819</v>
       </c>
       <c r="O8" t="n">
-        <v>6.990313987456502</v>
+        <v>6.983319109696204</v>
       </c>
       <c r="P8" t="n">
-        <v>268.9034619323799</v>
+        <v>268.8923833133667</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34044,28 +34117,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1884310009222113</v>
+        <v>-0.1876288678046499</v>
       </c>
       <c r="J9" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K9" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04072830385016124</v>
+        <v>0.04060236227344804</v>
       </c>
       <c r="M9" t="n">
-        <v>5.088765516262894</v>
+        <v>5.081305852160109</v>
       </c>
       <c r="N9" t="n">
-        <v>45.82061428856033</v>
+        <v>45.72504119295061</v>
       </c>
       <c r="O9" t="n">
-        <v>6.769092574973423</v>
+        <v>6.762029369423843</v>
       </c>
       <c r="P9" t="n">
-        <v>264.5691056403071</v>
+        <v>264.5606372817956</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34116,28 +34189,28 @@
         <v>0.0355</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2725789410827575</v>
+        <v>-0.2718721483889303</v>
       </c>
       <c r="J10" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K10" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06949716637900116</v>
+        <v>0.06950752520484116</v>
       </c>
       <c r="M10" t="n">
-        <v>5.689524733552438</v>
+        <v>5.680573063889557</v>
       </c>
       <c r="N10" t="n">
-        <v>54.50622358220004</v>
+        <v>54.38985789333336</v>
       </c>
       <c r="O10" t="n">
-        <v>7.382833032258013</v>
+        <v>7.374947992584989</v>
       </c>
       <c r="P10" t="n">
-        <v>269.5530374442779</v>
+        <v>269.5455756230496</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34188,28 +34261,28 @@
         <v>0.0356</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1150309675460206</v>
+        <v>0.1141048380910878</v>
       </c>
       <c r="J11" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K11" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01186476569049311</v>
+        <v>0.01173805310249543</v>
       </c>
       <c r="M11" t="n">
-        <v>6.052945721198204</v>
+        <v>6.043875045610264</v>
       </c>
       <c r="N11" t="n">
-        <v>60.38063213571172</v>
+        <v>60.2547887190124</v>
       </c>
       <c r="O11" t="n">
-        <v>7.770497547500528</v>
+        <v>7.762395810509304</v>
       </c>
       <c r="P11" t="n">
-        <v>263.8581369730485</v>
+        <v>263.8679143978683</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34260,28 +34333,28 @@
         <v>0.0356</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04751201040517419</v>
+        <v>-0.04872555480465309</v>
       </c>
       <c r="J12" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K12" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003040303948092737</v>
+        <v>0.003213321684499726</v>
       </c>
       <c r="M12" t="n">
-        <v>5.223350843196447</v>
+        <v>5.21685976068494</v>
       </c>
       <c r="N12" t="n">
-        <v>40.55816553356197</v>
+        <v>40.48266108163355</v>
       </c>
       <c r="O12" t="n">
-        <v>6.368529306956353</v>
+        <v>6.362598610759094</v>
       </c>
       <c r="P12" t="n">
-        <v>264.8598447236883</v>
+        <v>264.8726564737823</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34332,28 +34405,28 @@
         <v>0.0309</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09176931631376087</v>
+        <v>-0.09187569699090066</v>
       </c>
       <c r="J13" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K13" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006453109683928648</v>
+        <v>0.006503059068866279</v>
       </c>
       <c r="M13" t="n">
-        <v>6.516197909497812</v>
+        <v>6.502200013411565</v>
       </c>
       <c r="N13" t="n">
-        <v>71.04363993653337</v>
+        <v>70.8855274934303</v>
       </c>
       <c r="O13" t="n">
-        <v>8.428738929195362</v>
+        <v>8.419354339462753</v>
       </c>
       <c r="P13" t="n">
-        <v>271.1599833364593</v>
+        <v>271.1611064289897</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34404,28 +34477,28 @@
         <v>0.0304</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.002608994542351515</v>
+        <v>-0.004020668082092586</v>
       </c>
       <c r="J14" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K14" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L14" t="n">
-        <v>5.975009624958894e-06</v>
+        <v>1.426297506501584e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>6.118956879519694</v>
+        <v>6.111268843779036</v>
       </c>
       <c r="N14" t="n">
-        <v>62.41888804704037</v>
+        <v>62.29993217634637</v>
       </c>
       <c r="O14" t="n">
-        <v>7.900562514596057</v>
+        <v>7.893030607842996</v>
       </c>
       <c r="P14" t="n">
-        <v>272.5807167980103</v>
+        <v>272.5956202565185</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34476,28 +34549,28 @@
         <v>0.0251</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2512342775820528</v>
+        <v>-0.2525972911760755</v>
       </c>
       <c r="J15" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K15" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05095601865788468</v>
+        <v>0.05173415572063922</v>
       </c>
       <c r="M15" t="n">
-        <v>5.965573258573875</v>
+        <v>5.957944669343701</v>
       </c>
       <c r="N15" t="n">
-        <v>64.41092374615891</v>
+        <v>64.2861720659631</v>
       </c>
       <c r="O15" t="n">
-        <v>8.025641640776076</v>
+        <v>8.017865804936068</v>
       </c>
       <c r="P15" t="n">
-        <v>286.478606398304</v>
+        <v>286.4929961392552</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34548,28 +34621,28 @@
         <v>0.0256</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4193199320592366</v>
+        <v>-0.4194417862839735</v>
       </c>
       <c r="J16" t="n">
+        <v>449</v>
+      </c>
+      <c r="K16" t="n">
         <v>448</v>
       </c>
-      <c r="K16" t="n">
-        <v>447</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1323515624998317</v>
+        <v>0.1330442950655107</v>
       </c>
       <c r="M16" t="n">
-        <v>6.131497139567588</v>
+        <v>6.118421607208142</v>
       </c>
       <c r="N16" t="n">
-        <v>63.23704183741606</v>
+        <v>63.09603753221212</v>
       </c>
       <c r="O16" t="n">
-        <v>7.952172145861535</v>
+        <v>7.943301425239516</v>
       </c>
       <c r="P16" t="n">
-        <v>287.2002846908779</v>
+        <v>287.2015711857401</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34620,28 +34693,28 @@
         <v>0.0307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1761432312036731</v>
+        <v>-0.1715422166743069</v>
       </c>
       <c r="J17" t="n">
+        <v>449</v>
+      </c>
+      <c r="K17" t="n">
         <v>448</v>
       </c>
-      <c r="K17" t="n">
-        <v>447</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.02719465026782275</v>
+        <v>0.02587735742107133</v>
       </c>
       <c r="M17" t="n">
-        <v>6.557662990847327</v>
+        <v>6.565684412429592</v>
       </c>
       <c r="N17" t="n">
-        <v>60.88919131382517</v>
+        <v>60.96685536841381</v>
       </c>
       <c r="O17" t="n">
-        <v>7.803152652218536</v>
+        <v>7.808127519989271</v>
       </c>
       <c r="P17" t="n">
-        <v>278.9299972810141</v>
+        <v>278.8814213570752</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34692,28 +34765,28 @@
         <v>0.0496</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2242901147459413</v>
+        <v>0.2275690663998667</v>
       </c>
       <c r="J18" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K18" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0378195556667309</v>
+        <v>0.03903567009119102</v>
       </c>
       <c r="M18" t="n">
-        <v>6.543459630308737</v>
+        <v>6.547097579280752</v>
       </c>
       <c r="N18" t="n">
-        <v>70.3410081300806</v>
+        <v>70.29240317207542</v>
       </c>
       <c r="O18" t="n">
-        <v>8.386954639801065</v>
+        <v>8.38405648669398</v>
       </c>
       <c r="P18" t="n">
-        <v>263.6508122832229</v>
+        <v>263.6162080602663</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34751,7 +34824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S449"/>
+  <dimension ref="A1:S450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78291,6 +78364,103 @@
         </is>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:25+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>-40.8329921192177,172.875662589192</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>-40.83298765452281,172.87471362179684</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>-40.83302707503786,172.87374753620028</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-40.83302023317578,172.87279869308645</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>-40.833042480923865,172.87184986551867</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>-40.8329854058559,172.87095198998225</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>-40.832904720924226,172.87000778050532</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>-40.83282314716595,172.8691103279564</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>-40.83270338433901,172.86817352258942</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>-40.83259520021203,172.86723534775672</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>-40.83250839079847,172.86633793521278</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>-40.83230276456405,172.865424208101</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>-40.8321544071201,172.86451080087593</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>-40.831937972656654,172.8636016355703</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>-40.831795983303714,172.8626704747221</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>-40.83158357320028,172.8617342279566</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>-40.83151502600691,172.86078573047328</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0571/nzd0571.xlsx
+++ b/data/nzd0571/nzd0571.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S450"/>
+  <dimension ref="A1:S452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28804,6 +28804,132 @@
       <c r="S450" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>262.58</v>
+      </c>
+      <c r="C451" t="n">
+        <v>261.14</v>
+      </c>
+      <c r="D451" t="n">
+        <v>255.26</v>
+      </c>
+      <c r="E451" t="n">
+        <v>256.06</v>
+      </c>
+      <c r="F451" t="n">
+        <v>253.43</v>
+      </c>
+      <c r="G451" t="n">
+        <v>256.34</v>
+      </c>
+      <c r="H451" t="n">
+        <v>259.59</v>
+      </c>
+      <c r="I451" t="n">
+        <v>261.48</v>
+      </c>
+      <c r="J451" t="n">
+        <v>264.96</v>
+      </c>
+      <c r="K451" t="n">
+        <v>265.55</v>
+      </c>
+      <c r="L451" t="n">
+        <v>261.65</v>
+      </c>
+      <c r="M451" t="n">
+        <v>268.79</v>
+      </c>
+      <c r="N451" t="n">
+        <v>270.48</v>
+      </c>
+      <c r="O451" t="n">
+        <v>277.08</v>
+      </c>
+      <c r="P451" t="n">
+        <v>276.33</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>284.66</v>
+      </c>
+      <c r="R451" t="n">
+        <v>277.73</v>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>266.45</v>
+      </c>
+      <c r="C452" t="n">
+        <v>264.02</v>
+      </c>
+      <c r="D452" t="n">
+        <v>259.44</v>
+      </c>
+      <c r="E452" t="n">
+        <v>257.06</v>
+      </c>
+      <c r="F452" t="n">
+        <v>256.94</v>
+      </c>
+      <c r="G452" t="n">
+        <v>258.42</v>
+      </c>
+      <c r="H452" t="n">
+        <v>263.56</v>
+      </c>
+      <c r="I452" t="n">
+        <v>266.64</v>
+      </c>
+      <c r="J452" t="n">
+        <v>268.98</v>
+      </c>
+      <c r="K452" t="n">
+        <v>270.62</v>
+      </c>
+      <c r="L452" t="n">
+        <v>262.12</v>
+      </c>
+      <c r="M452" t="n">
+        <v>268.21</v>
+      </c>
+      <c r="N452" t="n">
+        <v>268.56</v>
+      </c>
+      <c r="O452" t="n">
+        <v>279.38</v>
+      </c>
+      <c r="P452" t="n">
+        <v>274.08</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>284.05</v>
+      </c>
+      <c r="R452" t="n">
+        <v>278.63</v>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28818,7 +28944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B463"/>
+  <dimension ref="A1:B465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33451,6 +33577,26 @@
       </c>
       <c r="B463" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>-0.88</v>
       </c>
     </row>
   </sheetData>
@@ -33613,28 +33759,28 @@
         <v>0.0407</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4314396955113928</v>
+        <v>-0.4295478585031937</v>
       </c>
       <c r="J2" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K2" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2098382246629781</v>
+        <v>0.2100332290411464</v>
       </c>
       <c r="M2" t="n">
-        <v>4.482372146765901</v>
+        <v>4.470917635301196</v>
       </c>
       <c r="N2" t="n">
-        <v>38.52823031848719</v>
+        <v>38.39222762398872</v>
       </c>
       <c r="O2" t="n">
-        <v>6.207111270026274</v>
+        <v>6.196146191302197</v>
       </c>
       <c r="P2" t="n">
-        <v>274.1143333024777</v>
+        <v>274.0942768972146</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33685,28 +33831,28 @@
         <v>0.0375</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3227628328725139</v>
+        <v>-0.3205771332077428</v>
       </c>
       <c r="J3" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K3" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1055169203631013</v>
+        <v>0.1051957605229887</v>
       </c>
       <c r="M3" t="n">
-        <v>5.102185097579519</v>
+        <v>5.088272018147725</v>
       </c>
       <c r="N3" t="n">
-        <v>48.54276455336762</v>
+        <v>48.36088703770798</v>
       </c>
       <c r="O3" t="n">
-        <v>6.96726377808158</v>
+        <v>6.954199237705804</v>
       </c>
       <c r="P3" t="n">
-        <v>268.9286836999115</v>
+        <v>268.9055219946044</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33757,28 +33903,28 @@
         <v>0.0406</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3755269621085064</v>
+        <v>-0.3736590985704235</v>
       </c>
       <c r="J4" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K4" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1153612551085829</v>
+        <v>0.1153891554684291</v>
       </c>
       <c r="M4" t="n">
-        <v>5.301689010165667</v>
+        <v>5.286812517126715</v>
       </c>
       <c r="N4" t="n">
-        <v>59.44231002780308</v>
+        <v>59.21582290665013</v>
       </c>
       <c r="O4" t="n">
-        <v>7.709883917920106</v>
+        <v>7.695181798154618</v>
       </c>
       <c r="P4" t="n">
-        <v>265.4671427759708</v>
+        <v>265.4473383095485</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33829,28 +33975,28 @@
         <v>0.0409</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3013979371853034</v>
+        <v>-0.301701468850417</v>
       </c>
       <c r="J5" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K5" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08888795752307543</v>
+        <v>0.08993451272552366</v>
       </c>
       <c r="M5" t="n">
-        <v>4.683273188494776</v>
+        <v>4.664940351632508</v>
       </c>
       <c r="N5" t="n">
-        <v>51.18195346882892</v>
+        <v>50.95660543930525</v>
       </c>
       <c r="O5" t="n">
-        <v>7.154156377157891</v>
+        <v>7.138389555026067</v>
       </c>
       <c r="P5" t="n">
-        <v>265.0102678608474</v>
+        <v>265.0134754272547</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33901,28 +34047,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.402609631350098</v>
+        <v>-0.4041962060258736</v>
       </c>
       <c r="J6" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K6" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2233283435420736</v>
+        <v>0.2264442871782527</v>
       </c>
       <c r="M6" t="n">
-        <v>4.226068949424115</v>
+        <v>4.213428021957612</v>
       </c>
       <c r="N6" t="n">
-        <v>30.98627553314508</v>
+        <v>30.87550542769339</v>
       </c>
       <c r="O6" t="n">
-        <v>5.566531732878659</v>
+        <v>5.556573173071096</v>
       </c>
       <c r="P6" t="n">
-        <v>267.7481712861724</v>
+        <v>267.7649486918092</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33973,28 +34119,28 @@
         <v>0.0404</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6299020326588487</v>
+        <v>-0.6285804295831756</v>
       </c>
       <c r="J7" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K7" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3024630535480091</v>
+        <v>0.3038144121409184</v>
       </c>
       <c r="M7" t="n">
-        <v>5.10536357099377</v>
+        <v>5.08958620623337</v>
       </c>
       <c r="N7" t="n">
-        <v>50.29772588444265</v>
+        <v>50.08846799930702</v>
       </c>
       <c r="O7" t="n">
-        <v>7.092088964786232</v>
+        <v>7.077320679417248</v>
       </c>
       <c r="P7" t="n">
-        <v>272.9409350795921</v>
+        <v>272.9269278161767</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34045,28 +34191,28 @@
         <v>0.0415</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4588646232814018</v>
+        <v>-0.4541670868943711</v>
       </c>
       <c r="J8" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K8" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L8" t="n">
-        <v>0.191808233403133</v>
+        <v>0.1898990711592995</v>
       </c>
       <c r="M8" t="n">
-        <v>5.192413219326397</v>
+        <v>5.191305783463326</v>
       </c>
       <c r="N8" t="n">
-        <v>48.76674578784819</v>
+        <v>48.67959841259921</v>
       </c>
       <c r="O8" t="n">
-        <v>6.983319109696204</v>
+        <v>6.977076638005291</v>
       </c>
       <c r="P8" t="n">
-        <v>268.8923833133667</v>
+        <v>268.8426178639768</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34117,28 +34263,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1876288678046499</v>
+        <v>-0.183389688915106</v>
       </c>
       <c r="J9" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K9" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04060236227344804</v>
+        <v>0.03916751775811711</v>
       </c>
       <c r="M9" t="n">
-        <v>5.081305852160109</v>
+        <v>5.079091461253703</v>
       </c>
       <c r="N9" t="n">
-        <v>45.72504119295061</v>
+        <v>45.64264839647809</v>
       </c>
       <c r="O9" t="n">
-        <v>6.762029369423843</v>
+        <v>6.755934309662734</v>
       </c>
       <c r="P9" t="n">
-        <v>264.5606372817956</v>
+        <v>264.5157177577256</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34189,28 +34335,28 @@
         <v>0.0355</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2718721483889303</v>
+        <v>-0.267454300363546</v>
       </c>
       <c r="J10" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K10" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06950752520484116</v>
+        <v>0.06796843578499545</v>
       </c>
       <c r="M10" t="n">
-        <v>5.680573063889557</v>
+        <v>5.678352429383475</v>
       </c>
       <c r="N10" t="n">
-        <v>54.38985789333336</v>
+        <v>54.26526107115271</v>
       </c>
       <c r="O10" t="n">
-        <v>7.374947992584989</v>
+        <v>7.366495847494432</v>
       </c>
       <c r="P10" t="n">
-        <v>269.5455756230496</v>
+        <v>269.4987714168236</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34261,28 +34407,28 @@
         <v>0.0356</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1141048380910878</v>
+        <v>0.1151698882388145</v>
       </c>
       <c r="J11" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K11" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01173805310249543</v>
+        <v>0.01207792506717298</v>
       </c>
       <c r="M11" t="n">
-        <v>6.043875045610264</v>
+        <v>6.02827586827982</v>
       </c>
       <c r="N11" t="n">
-        <v>60.2547887190124</v>
+        <v>60.02160863673469</v>
       </c>
       <c r="O11" t="n">
-        <v>7.762395810509304</v>
+        <v>7.747361398355874</v>
       </c>
       <c r="P11" t="n">
-        <v>263.8679143978683</v>
+        <v>263.856605217279</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34333,28 +34479,28 @@
         <v>0.0356</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04872555480465309</v>
+        <v>-0.05027928618605448</v>
       </c>
       <c r="J12" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K12" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003213321684499726</v>
+        <v>0.003457008363982106</v>
       </c>
       <c r="M12" t="n">
-        <v>5.21685976068494</v>
+        <v>5.200234253088703</v>
       </c>
       <c r="N12" t="n">
-        <v>40.48266108163355</v>
+        <v>40.31560642247762</v>
       </c>
       <c r="O12" t="n">
-        <v>6.362598610759094</v>
+        <v>6.349457175418826</v>
       </c>
       <c r="P12" t="n">
-        <v>264.8726564737823</v>
+        <v>264.8891053694694</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34405,28 +34551,28 @@
         <v>0.0309</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09187569699090066</v>
+        <v>-0.09204802226964411</v>
       </c>
       <c r="J13" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K13" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006503059068866279</v>
+        <v>0.006598157585086639</v>
       </c>
       <c r="M13" t="n">
-        <v>6.502200013411565</v>
+        <v>6.474665115100616</v>
       </c>
       <c r="N13" t="n">
-        <v>70.8855274934303</v>
+        <v>70.57170044647221</v>
       </c>
       <c r="O13" t="n">
-        <v>8.419354339462753</v>
+        <v>8.400696426277538</v>
       </c>
       <c r="P13" t="n">
-        <v>271.1611064289897</v>
+        <v>271.1629347548478</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34477,28 +34623,28 @@
         <v>0.0304</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.004020668082092586</v>
+        <v>-0.006780085271477043</v>
       </c>
       <c r="J14" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K14" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L14" t="n">
-        <v>1.426297506501584e-05</v>
+        <v>4.097288218429807e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>6.111268843779036</v>
+        <v>6.095632473492726</v>
       </c>
       <c r="N14" t="n">
-        <v>62.29993217634637</v>
+        <v>62.06623240996576</v>
       </c>
       <c r="O14" t="n">
-        <v>7.893030607842996</v>
+        <v>7.878212513633137</v>
       </c>
       <c r="P14" t="n">
-        <v>272.5956202565185</v>
+        <v>272.6248507312225</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34549,28 +34695,28 @@
         <v>0.0251</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2525972911760755</v>
+        <v>-0.2539469718474094</v>
       </c>
       <c r="J15" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K15" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05173415572063922</v>
+        <v>0.05278878365876294</v>
       </c>
       <c r="M15" t="n">
-        <v>5.957944669343701</v>
+        <v>5.937073593756197</v>
       </c>
       <c r="N15" t="n">
-        <v>64.2861720659631</v>
+        <v>64.01630967627676</v>
       </c>
       <c r="O15" t="n">
-        <v>8.017865804936068</v>
+        <v>8.001019289832813</v>
       </c>
       <c r="P15" t="n">
-        <v>286.4929961392552</v>
+        <v>286.5072727939307</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34621,28 +34767,28 @@
         <v>0.0256</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4194417862839735</v>
+        <v>-0.4200865693059098</v>
       </c>
       <c r="J16" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K16" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1330442950655107</v>
+        <v>0.1346458304316563</v>
       </c>
       <c r="M16" t="n">
-        <v>6.118421607208142</v>
+        <v>6.096323302379672</v>
       </c>
       <c r="N16" t="n">
-        <v>63.09603753221212</v>
+        <v>62.82318657899521</v>
       </c>
       <c r="O16" t="n">
-        <v>7.943301425239516</v>
+        <v>7.926107908614115</v>
       </c>
       <c r="P16" t="n">
-        <v>287.2015711857401</v>
+        <v>287.2084128413616</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34693,28 +34839,28 @@
         <v>0.0307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1715422166743069</v>
+        <v>-0.1621663874310133</v>
       </c>
       <c r="J17" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K17" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02587735742107133</v>
+        <v>0.02327002047868532</v>
       </c>
       <c r="M17" t="n">
-        <v>6.565684412429592</v>
+        <v>6.582192118672757</v>
       </c>
       <c r="N17" t="n">
-        <v>60.96685536841381</v>
+        <v>61.14216644628902</v>
       </c>
       <c r="O17" t="n">
-        <v>7.808127519989271</v>
+        <v>7.819345653332446</v>
       </c>
       <c r="P17" t="n">
-        <v>278.8814213570752</v>
+        <v>278.7821439416526</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34765,28 +34911,28 @@
         <v>0.0496</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2275690663998667</v>
+        <v>0.2354020055243743</v>
       </c>
       <c r="J18" t="n">
+        <v>451</v>
+      </c>
+      <c r="K18" t="n">
         <v>449</v>
       </c>
-      <c r="K18" t="n">
-        <v>447</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.03903567009119102</v>
+        <v>0.04191130875888449</v>
       </c>
       <c r="M18" t="n">
-        <v>6.547097579280752</v>
+        <v>6.561137570381291</v>
       </c>
       <c r="N18" t="n">
-        <v>70.29240317207542</v>
+        <v>70.29205041203664</v>
       </c>
       <c r="O18" t="n">
-        <v>8.38405648669398</v>
+        <v>8.384035449116174</v>
       </c>
       <c r="P18" t="n">
-        <v>263.6162080602663</v>
+        <v>263.5332912593989</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34824,7 +34970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S450"/>
+  <dimension ref="A1:S452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78461,6 +78607,200 @@
         </is>
       </c>
     </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>-40.83299040808844,172.87566264275694</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>-40.832986123512846,172.87471366974523</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>-40.833024192321865,172.87374753459926</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-40.83301699012035,172.87279869133152</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>-40.83304067922643,172.87184986456938</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>-40.83297974611348,172.8709525437061</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>-40.832897443619224,172.87000848363914</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>-40.83282082658129,172.86911074600002</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>-40.832692494087176,172.868175471097</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>-40.83259002290858,172.8672362743793</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>-40.83250255739957,172.86633944878665</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>-40.8322999362552,172.86542494199153</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>-40.83214577763985,172.86451325382853</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>-40.83193568320781,172.86360228638281</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>-40.831790170498685,172.86267211989315</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>-40.83157790731381,172.86173563238967</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>-40.83150573043095,172.8607880347512</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>-40.8329555550872,172.87566373378974</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>-40.832960186402865,172.87471448204644</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>-40.83298653684411,172.87374751368574</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-40.833007981633,172.87279868645672</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>-40.83300905943646,172.8718498479096</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>-40.83296105997972,172.87095437187298</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>-40.8328617758402,172.87001192986068</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>-40.83277477190036,172.86911904255135</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>-40.832656609814386,172.86818189158475</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>-40.83254476613472,172.86724437433253</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>-40.83249840331246,172.86634052663456</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>-40.832305062564984,172.86542361181486</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>-40.8321626843766,172.86450844804324</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>-40.83191543039085,172.86360804356863</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>-40.83180998687929,172.86266651135446</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>-40.831583307611844,172.8617342937894</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>-40.83149776279436,172.86079000984603</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0571/nzd0571.xlsx
+++ b/data/nzd0571/nzd0571.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S452"/>
+  <dimension ref="A1:S455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28910,7 +28910,7 @@
         <v>262.12</v>
       </c>
       <c r="M452" t="n">
-        <v>268.21</v>
+        <v>273.43</v>
       </c>
       <c r="N452" t="n">
         <v>268.56</v>
@@ -28928,6 +28928,195 @@
         <v>278.63</v>
       </c>
       <c r="S452" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>267.16</v>
+      </c>
+      <c r="C453" t="n">
+        <v>264.83</v>
+      </c>
+      <c r="D453" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="E453" t="n">
+        <v>258.16</v>
+      </c>
+      <c r="F453" t="n">
+        <v>257.33</v>
+      </c>
+      <c r="G453" t="n">
+        <v>258.68</v>
+      </c>
+      <c r="H453" t="n">
+        <v>263.52</v>
+      </c>
+      <c r="I453" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="J453" t="n">
+        <v>269.21</v>
+      </c>
+      <c r="K453" t="n">
+        <v>270.99</v>
+      </c>
+      <c r="L453" t="n">
+        <v>263.16</v>
+      </c>
+      <c r="M453" t="n">
+        <v>274.4</v>
+      </c>
+      <c r="N453" t="n">
+        <v>269.84</v>
+      </c>
+      <c r="O453" t="n">
+        <v>280.5</v>
+      </c>
+      <c r="P453" t="n">
+        <v>276.06</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>285.85</v>
+      </c>
+      <c r="R453" t="n">
+        <v>278.91</v>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:52+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>266.98</v>
+      </c>
+      <c r="C454" t="n">
+        <v>264.99</v>
+      </c>
+      <c r="D454" t="n">
+        <v>260.59</v>
+      </c>
+      <c r="E454" t="n">
+        <v>257.66</v>
+      </c>
+      <c r="F454" t="n">
+        <v>257.3</v>
+      </c>
+      <c r="G454" t="n">
+        <v>258.84</v>
+      </c>
+      <c r="H454" t="n">
+        <v>264.11</v>
+      </c>
+      <c r="I454" t="n">
+        <v>266.46</v>
+      </c>
+      <c r="J454" t="n">
+        <v>269.24</v>
+      </c>
+      <c r="K454" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="L454" t="n">
+        <v>263.51</v>
+      </c>
+      <c r="M454" t="n">
+        <v>276.66</v>
+      </c>
+      <c r="N454" t="n">
+        <v>270.68</v>
+      </c>
+      <c r="O454" t="n">
+        <v>283.67</v>
+      </c>
+      <c r="P454" t="n">
+        <v>280.49</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="R454" t="n">
+        <v>278.1</v>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>265.18</v>
+      </c>
+      <c r="C455" t="n">
+        <v>262.37</v>
+      </c>
+      <c r="D455" t="n">
+        <v>259</v>
+      </c>
+      <c r="E455" t="n">
+        <v>257.84</v>
+      </c>
+      <c r="F455" t="n">
+        <v>257.72</v>
+      </c>
+      <c r="G455" t="n">
+        <v>259.69</v>
+      </c>
+      <c r="H455" t="n">
+        <v>263.36</v>
+      </c>
+      <c r="I455" t="n">
+        <v>264.24</v>
+      </c>
+      <c r="J455" t="n">
+        <v>267.83</v>
+      </c>
+      <c r="K455" t="n">
+        <v>272.51</v>
+      </c>
+      <c r="L455" t="n">
+        <v>263.87</v>
+      </c>
+      <c r="M455" t="n">
+        <v>277.42</v>
+      </c>
+      <c r="N455" t="n">
+        <v>266.75</v>
+      </c>
+      <c r="O455" t="n">
+        <v>283.42</v>
+      </c>
+      <c r="P455" t="n">
+        <v>280.97</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>286.87</v>
+      </c>
+      <c r="R455" t="n">
+        <v>278.94</v>
+      </c>
+      <c r="S455" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28944,7 +29133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B465"/>
+  <dimension ref="A1:B468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33597,6 +33786,36 @@
       </c>
       <c r="B465" t="n">
         <v>-0.88</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>-0.37</v>
       </c>
     </row>
   </sheetData>
@@ -33759,28 +33978,28 @@
         <v>0.0407</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4295478585031937</v>
+        <v>-0.4241146046761238</v>
       </c>
       <c r="J2" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K2" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2100332290411464</v>
+        <v>0.208035754632413</v>
       </c>
       <c r="M2" t="n">
-        <v>4.470917635301196</v>
+        <v>4.466106247048054</v>
       </c>
       <c r="N2" t="n">
-        <v>38.39222762398872</v>
+        <v>38.24498209832998</v>
       </c>
       <c r="O2" t="n">
-        <v>6.196146191302197</v>
+        <v>6.184252751814886</v>
       </c>
       <c r="P2" t="n">
-        <v>274.0942768972146</v>
+        <v>274.0365547808161</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33831,28 +34050,28 @@
         <v>0.0375</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3205771332077428</v>
+        <v>-0.3153239421038719</v>
       </c>
       <c r="J3" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K3" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1051957605229887</v>
+        <v>0.1034166113271212</v>
       </c>
       <c r="M3" t="n">
-        <v>5.088272018147725</v>
+        <v>5.076017098327621</v>
       </c>
       <c r="N3" t="n">
-        <v>48.36088703770798</v>
+        <v>48.14538828684942</v>
       </c>
       <c r="O3" t="n">
-        <v>6.954199237705804</v>
+        <v>6.938687792864688</v>
       </c>
       <c r="P3" t="n">
-        <v>268.9055219946044</v>
+        <v>268.8497154118194</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33903,28 +34122,28 @@
         <v>0.0406</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3736590985704235</v>
+        <v>-0.3675539903987761</v>
       </c>
       <c r="J4" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K4" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1153891554684291</v>
+        <v>0.1134639511584881</v>
       </c>
       <c r="M4" t="n">
-        <v>5.286812517126715</v>
+        <v>5.278740433586889</v>
       </c>
       <c r="N4" t="n">
-        <v>59.21582290665013</v>
+        <v>58.95507479655231</v>
       </c>
       <c r="O4" t="n">
-        <v>7.695181798154618</v>
+        <v>7.678220809312031</v>
       </c>
       <c r="P4" t="n">
-        <v>265.4473383095485</v>
+        <v>265.3824691299371</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33975,28 +34194,28 @@
         <v>0.0409</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.301701468850417</v>
+        <v>-0.300287051950163</v>
       </c>
       <c r="J5" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K5" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08993451272552366</v>
+        <v>0.0904782988478563</v>
       </c>
       <c r="M5" t="n">
-        <v>4.664940351632508</v>
+        <v>4.639958312592792</v>
       </c>
       <c r="N5" t="n">
-        <v>50.95660543930525</v>
+        <v>50.62700843016511</v>
       </c>
       <c r="O5" t="n">
-        <v>7.138389555026067</v>
+        <v>7.115265872064453</v>
       </c>
       <c r="P5" t="n">
-        <v>265.0134754272547</v>
+        <v>264.9984482996434</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34047,28 +34266,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4041962060258736</v>
+        <v>-0.4033523039230956</v>
       </c>
       <c r="J6" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K6" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2264442871782527</v>
+        <v>0.2285349883705431</v>
       </c>
       <c r="M6" t="n">
-        <v>4.213428021957612</v>
+        <v>4.190460803887701</v>
       </c>
       <c r="N6" t="n">
-        <v>30.87550542769339</v>
+        <v>30.67418499127571</v>
       </c>
       <c r="O6" t="n">
-        <v>5.556573173071096</v>
+        <v>5.53842802528621</v>
       </c>
       <c r="P6" t="n">
-        <v>267.7649486918092</v>
+        <v>267.755979157791</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34119,28 +34338,28 @@
         <v>0.0404</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6285804295831756</v>
+        <v>-0.6242666583626066</v>
       </c>
       <c r="J7" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K7" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3038144121409184</v>
+        <v>0.3040438099959119</v>
       </c>
       <c r="M7" t="n">
-        <v>5.08958620623337</v>
+        <v>5.078070142641235</v>
       </c>
       <c r="N7" t="n">
-        <v>50.08846799930702</v>
+        <v>49.8226048573904</v>
       </c>
       <c r="O7" t="n">
-        <v>7.077320679417248</v>
+        <v>7.058512935271168</v>
       </c>
       <c r="P7" t="n">
-        <v>272.9269278161767</v>
+        <v>272.88108408334</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34191,28 +34410,28 @@
         <v>0.0415</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4541670868943711</v>
+        <v>-0.4444177292799263</v>
       </c>
       <c r="J8" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K8" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1898990711592995</v>
+        <v>0.1847291461412788</v>
       </c>
       <c r="M8" t="n">
-        <v>5.191305783463326</v>
+        <v>5.202687953687466</v>
       </c>
       <c r="N8" t="n">
-        <v>48.67959841259921</v>
+        <v>48.68438176589816</v>
       </c>
       <c r="O8" t="n">
-        <v>6.977076638005291</v>
+        <v>6.977419420236837</v>
       </c>
       <c r="P8" t="n">
-        <v>268.8426178639768</v>
+        <v>268.7390221276634</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34263,28 +34482,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.183389688915106</v>
+        <v>-0.174688820409289</v>
       </c>
       <c r="J9" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K9" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03916751775811711</v>
+        <v>0.03602276436695806</v>
       </c>
       <c r="M9" t="n">
-        <v>5.079091461253703</v>
+        <v>5.086846975994577</v>
       </c>
       <c r="N9" t="n">
-        <v>45.64264839647809</v>
+        <v>45.61003221594998</v>
       </c>
       <c r="O9" t="n">
-        <v>6.755934309662734</v>
+        <v>6.753519987084512</v>
       </c>
       <c r="P9" t="n">
-        <v>264.5157177577256</v>
+        <v>264.4232791666764</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34335,28 +34554,28 @@
         <v>0.0355</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.267454300363546</v>
+        <v>-0.258541335251478</v>
       </c>
       <c r="J10" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K10" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06796843578499545</v>
+        <v>0.06446258508318992</v>
       </c>
       <c r="M10" t="n">
-        <v>5.678352429383475</v>
+        <v>5.686571093943313</v>
       </c>
       <c r="N10" t="n">
-        <v>54.26526107115271</v>
+        <v>54.18185026437929</v>
       </c>
       <c r="O10" t="n">
-        <v>7.366495847494432</v>
+        <v>7.360832172001973</v>
       </c>
       <c r="P10" t="n">
-        <v>269.4987714168236</v>
+        <v>269.4040706318388</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34407,28 +34626,28 @@
         <v>0.0356</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1151698882388145</v>
+        <v>0.1214168570272117</v>
       </c>
       <c r="J11" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K11" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01207792506717298</v>
+        <v>0.01359036733073393</v>
       </c>
       <c r="M11" t="n">
-        <v>6.02827586827982</v>
+        <v>6.017759312331795</v>
       </c>
       <c r="N11" t="n">
-        <v>60.02160863673469</v>
+        <v>59.76191372310918</v>
       </c>
       <c r="O11" t="n">
-        <v>7.747361398355874</v>
+        <v>7.73058301314391</v>
       </c>
       <c r="P11" t="n">
-        <v>263.856605217279</v>
+        <v>263.7902170678535</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34479,28 +34698,28 @@
         <v>0.0356</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05027928618605448</v>
+        <v>-0.05030446759914312</v>
       </c>
       <c r="J12" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K12" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003457008363982106</v>
+        <v>0.003516605605417999</v>
       </c>
       <c r="M12" t="n">
-        <v>5.200234253088703</v>
+        <v>5.167468744196382</v>
       </c>
       <c r="N12" t="n">
-        <v>40.31560642247762</v>
+        <v>40.04976106800731</v>
       </c>
       <c r="O12" t="n">
-        <v>6.349457175418826</v>
+        <v>6.328488055452685</v>
       </c>
       <c r="P12" t="n">
-        <v>264.8891053694694</v>
+        <v>264.8893685244041</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34551,28 +34770,28 @@
         <v>0.0309</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09204802226964411</v>
+        <v>-0.07939054211991084</v>
       </c>
       <c r="J13" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K13" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006598157585086639</v>
+        <v>0.004966884707276242</v>
       </c>
       <c r="M13" t="n">
-        <v>6.474665115100616</v>
+        <v>6.488240140475329</v>
       </c>
       <c r="N13" t="n">
-        <v>70.57170044647221</v>
+        <v>70.52310157643888</v>
       </c>
       <c r="O13" t="n">
-        <v>8.400696426277538</v>
+        <v>8.39780337805303</v>
       </c>
       <c r="P13" t="n">
-        <v>271.1629347548478</v>
+        <v>271.0284756375634</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34623,28 +34842,28 @@
         <v>0.0304</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.006780085271477043</v>
+        <v>-0.01138108478495016</v>
       </c>
       <c r="J14" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K14" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L14" t="n">
-        <v>4.097288218429807e-05</v>
+        <v>0.0001171489111837509</v>
       </c>
       <c r="M14" t="n">
-        <v>6.095632473492726</v>
+        <v>6.074812248933127</v>
       </c>
       <c r="N14" t="n">
-        <v>62.06623240996576</v>
+        <v>61.74738847667876</v>
       </c>
       <c r="O14" t="n">
-        <v>7.878212513633137</v>
+        <v>7.857950653744191</v>
       </c>
       <c r="P14" t="n">
-        <v>272.6248507312225</v>
+        <v>272.6737564421255</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34695,28 +34914,28 @@
         <v>0.0251</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2539469718474094</v>
+        <v>-0.2499734199669891</v>
       </c>
       <c r="J15" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K15" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05278878365876294</v>
+        <v>0.05197267376724735</v>
       </c>
       <c r="M15" t="n">
-        <v>5.937073593756197</v>
+        <v>5.9191703300417</v>
       </c>
       <c r="N15" t="n">
-        <v>64.01630967627676</v>
+        <v>63.66106113357892</v>
       </c>
       <c r="O15" t="n">
-        <v>8.001019289832813</v>
+        <v>7.978788199568837</v>
       </c>
       <c r="P15" t="n">
-        <v>286.5072727939307</v>
+        <v>286.4650295916139</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34767,28 +34986,28 @@
         <v>0.0256</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4200865693059098</v>
+        <v>-0.4155137679664348</v>
       </c>
       <c r="J16" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K16" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1346458304316563</v>
+        <v>0.1337847466083605</v>
       </c>
       <c r="M16" t="n">
-        <v>6.096323302379672</v>
+        <v>6.076386425247363</v>
       </c>
       <c r="N16" t="n">
-        <v>62.82318657899521</v>
+        <v>62.5114736950853</v>
       </c>
       <c r="O16" t="n">
-        <v>7.926107908614115</v>
+        <v>7.906419777312946</v>
       </c>
       <c r="P16" t="n">
-        <v>287.2084128413616</v>
+        <v>287.1597864337463</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34839,28 +35058,28 @@
         <v>0.0307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1621663874310133</v>
+        <v>-0.1457933625941103</v>
       </c>
       <c r="J17" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K17" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02327002047868532</v>
+        <v>0.01891281122078958</v>
       </c>
       <c r="M17" t="n">
-        <v>6.582192118672757</v>
+        <v>6.618501514135963</v>
       </c>
       <c r="N17" t="n">
-        <v>61.14216644628902</v>
+        <v>61.65903108854633</v>
       </c>
       <c r="O17" t="n">
-        <v>7.819345653332446</v>
+        <v>7.852326476181841</v>
       </c>
       <c r="P17" t="n">
-        <v>278.7821439416526</v>
+        <v>278.6081502129384</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34911,28 +35130,28 @@
         <v>0.0496</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2354020055243743</v>
+        <v>0.2474143628511698</v>
       </c>
       <c r="J18" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K18" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04191130875888449</v>
+        <v>0.04649438033830655</v>
       </c>
       <c r="M18" t="n">
-        <v>6.561137570381291</v>
+        <v>6.584382192530596</v>
       </c>
       <c r="N18" t="n">
-        <v>70.29205041203664</v>
+        <v>70.32342800647078</v>
       </c>
       <c r="O18" t="n">
-        <v>8.384035449116174</v>
+        <v>8.385906510716106</v>
       </c>
       <c r="P18" t="n">
-        <v>263.5332912593989</v>
+        <v>263.4056914139493</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34970,7 +35189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S452"/>
+  <dimension ref="A1:S455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78767,7 +78986,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>-40.832305062564984,172.86542361181486</t>
+          <t>-40.83225892577621,172.8654355833975</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -78796,6 +79015,297 @@
         </is>
       </c>
       <c r="S452" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>-40.832949160867315,172.87566393395323</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>-40.832952891590665,172.87471471050605</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-40.83298347395835,172.87374751198465</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-40.83299807229691,172.87279868109442</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>-40.83300554612646,172.8718498460585</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>-40.83295872421301,172.8709546003938</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>-40.8328621352133,172.87001189513805</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>-40.83277164803631,172.86911960530153</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>-40.8326545567341,172.8681822589259</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>-40.83254146337209,172.86724496545295</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>-40.83248921128986,172.86634291165922</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>-40.832250352464705,172.86543780800008</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>-40.832151413218796,172.8645116519004</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>-40.83190556814943,172.86361084706652</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>-40.83179254846437,172.86267144686866</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>-40.831567372306075,172.86173824375678</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>-40.831495283974085,172.8607906243199</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:52+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>-40.83295078193715,172.87566388320755</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>-40.8329514506401,172.87471475563387</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-40.832976177083445,172.873747507932</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-40.83300257654059,172.87279868353184</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>-40.83300581638107,172.87184984620092</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>-40.83295728681808,172.87095474102196</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>-40.8328568344602,172.87001240729663</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>-40.83277637845901,172.86911875313697</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>-40.83265428894101,172.86818230683994</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>-40.83254083852511,172.86724507728655</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>-40.8324861178207,172.8663437143116</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>-40.832230377532525,172.86544299109258</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>-40.83214401652142,172.86451375443104</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>-40.83187765448348,172.86361878196232</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>-40.83175353221184,172.8626824894491</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>-40.83156383112699,172.86173912152705</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>-40.83150245484703,172.86078884673466</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>-40.83296699263544,172.87566337575066</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>-40.832975046205476,172.87471401666562</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>-40.83299050057862,172.87374751588715</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-40.83300095501287,172.87279868265438</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-40.83300203281644,172.87184984420742</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>-40.83294965065762,172.87095548810902</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-40.83286357270565,172.87001175624758</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>-40.832796192682316,172.86911518369172</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>-40.83266687521587,172.8681800548788</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>-40.83252789526612,172.86724739383888</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>-40.832482935966716,172.8663445398968</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>-40.832223660298624,172.86544473407872</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>-40.832178622498006,172.86450391758714</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>-40.83187985587672,172.86361815618213</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>-40.83174930471712,172.8626836859356</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>-40.8315583422994,172.86174048207081</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>-40.83149501838619,172.86079069015636</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
